--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
@@ -1,218 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LevelInfo" sheetId="1" r:id="rId1"/>
+    <sheet name="LevelInfo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>level_exp</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>所需经验</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -512,158 +471,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -717,11 +677,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1010,145 +1033,201 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.5"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col width="11.5" customWidth="1" style="1" min="1" max="1"/>
+    <col width="17.5" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>level_exp</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sacrifice_num</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>所需经验</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>升级所需祭品数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B4" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="5">
+      <c r="A5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B6" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+    <row r="7">
+      <c r="A7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C7" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1000</v>
+    <row r="8">
+      <c r="A8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>2000</v>
+    <row r="9">
+      <c r="A9" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>4000</v>
+    <row r="10">
+      <c r="A10" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>8000</v>
+    <row r="11">
+      <c r="A11" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
+    <row r="12">
+      <c r="A12" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C12" t="n">
         <v>5</v>
       </c>
-      <c r="B8">
-        <v>16000</v>
-      </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>32000</v>
+    <row r="13">
+      <c r="A13" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>64000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>128000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>256000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>512000</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1"/>
-    <row r="15" ht="15" customHeight="1"/>
-    <row r="16" ht="15" customHeight="1"/>
-    <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="15" customHeight="1"/>
-    <row r="19" ht="15" customHeight="1"/>
-    <row r="20" ht="15" customHeight="1"/>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1"/>
-    <row r="23" ht="15" customHeight="1"/>
-    <row r="24" ht="15" customHeight="1"/>
-    <row r="56" ht="12" customHeight="1"/>
-    <row r="57" ht="12" customHeight="1"/>
-    <row r="58" ht="12" customHeight="1"/>
-    <row r="59" ht="12" customHeight="1"/>
-    <row r="60" ht="12" customHeight="1"/>
-    <row r="61" ht="12" customHeight="1"/>
-    <row r="62" ht="12" customHeight="1"/>
-    <row r="63" ht="12" customHeight="1"/>
-    <row r="64" ht="12" customHeight="1"/>
+    <row r="14" ht="15" customHeight="1" s="1"/>
+    <row r="15" ht="15" customHeight="1" s="1"/>
+    <row r="16" ht="15" customHeight="1" s="1"/>
+    <row r="17" ht="15" customHeight="1" s="1"/>
+    <row r="18" ht="15" customHeight="1" s="1"/>
+    <row r="19" ht="15" customHeight="1" s="1"/>
+    <row r="20" ht="15" customHeight="1" s="1"/>
+    <row r="21" ht="15" customHeight="1" s="1"/>
+    <row r="22" ht="15" customHeight="1" s="1"/>
+    <row r="23" ht="15" customHeight="1" s="1"/>
+    <row r="24" ht="15" customHeight="1" s="1"/>
+    <row r="56" ht="12" customHeight="1" s="1"/>
+    <row r="57" ht="12" customHeight="1" s="1"/>
+    <row r="58" ht="12" customHeight="1" s="1"/>
+    <row r="59" ht="12" customHeight="1" s="1"/>
+    <row r="60" ht="12" customHeight="1" s="1"/>
+    <row r="61" ht="12" customHeight="1" s="1"/>
+    <row r="62" ht="12" customHeight="1" s="1"/>
+    <row r="63" ht="12" customHeight="1" s="1"/>
+    <row r="64" ht="12" customHeight="1" s="1"/>
   </sheetData>
-  <sortState ref="A4:X88">
-    <sortCondition ref="A4"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
@@ -1,177 +1,227 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="LevelInfo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LevelInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>level_exp</t>
+  </si>
+  <si>
+    <t>sacrifice_num</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>所需经验</t>
+  </si>
+  <si>
+    <t>升级所需祭品数量</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -471,159 +521,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -677,74 +727,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1033,201 +1020,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C64"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col width="11.5" customWidth="1" style="1" min="1" max="1"/>
-    <col width="17.5" customWidth="1" style="1" min="2" max="2"/>
+    <col min="1" max="1" width="11.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>level_exp</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sacrifice_num</t>
-        </is>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>所需经验</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>升级所需祭品数量</t>
-        </is>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4">
         <v>100</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>1000</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>5000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7">
         <v>10000</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8">
         <v>50000</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9">
         <v>100000</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10">
         <v>500000</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11">
         <v>1000000</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>5</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0" t="n">
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12">
         <v>5000000</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>5</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="n">
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13">
         <v>10000000</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="1"/>
-    <row r="15" ht="15" customHeight="1" s="1"/>
-    <row r="16" ht="15" customHeight="1" s="1"/>
-    <row r="17" ht="15" customHeight="1" s="1"/>
-    <row r="18" ht="15" customHeight="1" s="1"/>
-    <row r="19" ht="15" customHeight="1" s="1"/>
-    <row r="20" ht="15" customHeight="1" s="1"/>
-    <row r="21" ht="15" customHeight="1" s="1"/>
-    <row r="22" ht="15" customHeight="1" s="1"/>
-    <row r="23" ht="15" customHeight="1" s="1"/>
-    <row r="24" ht="15" customHeight="1" s="1"/>
-    <row r="56" ht="12" customHeight="1" s="1"/>
-    <row r="57" ht="12" customHeight="1" s="1"/>
-    <row r="58" ht="12" customHeight="1" s="1"/>
-    <row r="59" ht="12" customHeight="1" s="1"/>
-    <row r="60" ht="12" customHeight="1" s="1"/>
-    <row r="61" ht="12" customHeight="1" s="1"/>
-    <row r="62" ht="12" customHeight="1" s="1"/>
-    <row r="63" ht="12" customHeight="1" s="1"/>
-    <row r="64" ht="12" customHeight="1" s="1"/>
+    <row r="14" ht="15" customHeight="1"/>
+    <row r="15" ht="15" customHeight="1"/>
+    <row r="16" ht="15" customHeight="1"/>
+    <row r="17" ht="15" customHeight="1"/>
+    <row r="18" ht="15" customHeight="1"/>
+    <row r="19" ht="15" customHeight="1"/>
+    <row r="20" ht="15" customHeight="1"/>
+    <row r="21" ht="15" customHeight="1"/>
+    <row r="22" ht="15" customHeight="1"/>
+    <row r="23" ht="15" customHeight="1"/>
+    <row r="24" ht="15" customHeight="1"/>
+    <row r="56" ht="12" customHeight="1"/>
+    <row r="57" ht="12" customHeight="1"/>
+    <row r="58" ht="12" customHeight="1"/>
+    <row r="59" ht="12" customHeight="1"/>
+    <row r="60" ht="12" customHeight="1"/>
+    <row r="61" ht="12" customHeight="1"/>
+    <row r="62" ht="12" customHeight="1"/>
+    <row r="63" ht="12" customHeight="1"/>
+    <row r="64" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
@@ -1,227 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LevelInfo" sheetId="1" r:id="rId1"/>
+    <sheet name="LevelInfo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>level_exp</t>
-  </si>
-  <si>
-    <t>sacrifice_num</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>所需经验</t>
-  </si>
-  <si>
-    <t>升级所需祭品数量</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -521,159 +471,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -727,11 +677,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1020,182 +1033,247 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col width="11.5" customWidth="1" style="1" min="1" max="1"/>
+    <col width="17.5" customWidth="1" style="1" min="2" max="2"/>
+    <col width="17.125" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>level_exp</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>sacrifice_num</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>attribute_point</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>所需经验</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>升级所需祭品数量</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>升级获得加点数</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B4" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B5" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+    <row r="6">
+      <c r="A6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B7" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+    <row r="8">
+      <c r="A8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B9" s="0" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B10" s="0" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B11" s="0" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
+    <row r="12">
+      <c r="A12" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="0" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1000</v>
-      </c>
-      <c r="C5">
+    <row r="13">
+      <c r="A13" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="0" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>5000</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>10000</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>50000</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>100000</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>500000</v>
-      </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>1000000</v>
-      </c>
-      <c r="C11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>5000000</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>10000000</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1"/>
-    <row r="15" ht="15" customHeight="1"/>
-    <row r="16" ht="15" customHeight="1"/>
-    <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="15" customHeight="1"/>
-    <row r="19" ht="15" customHeight="1"/>
-    <row r="20" ht="15" customHeight="1"/>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1"/>
-    <row r="23" ht="15" customHeight="1"/>
-    <row r="24" ht="15" customHeight="1"/>
-    <row r="56" ht="12" customHeight="1"/>
-    <row r="57" ht="12" customHeight="1"/>
-    <row r="58" ht="12" customHeight="1"/>
-    <row r="59" ht="12" customHeight="1"/>
-    <row r="60" ht="12" customHeight="1"/>
-    <row r="61" ht="12" customHeight="1"/>
-    <row r="62" ht="12" customHeight="1"/>
-    <row r="63" ht="12" customHeight="1"/>
-    <row r="64" ht="12" customHeight="1"/>
+    <row r="14" ht="15" customHeight="1" s="1"/>
+    <row r="15" ht="15" customHeight="1" s="1"/>
+    <row r="16" ht="15" customHeight="1" s="1"/>
+    <row r="17" ht="15" customHeight="1" s="1"/>
+    <row r="18" ht="15" customHeight="1" s="1"/>
+    <row r="19" ht="15" customHeight="1" s="1"/>
+    <row r="20" ht="15" customHeight="1" s="1"/>
+    <row r="21" ht="15" customHeight="1" s="1"/>
+    <row r="22" ht="15" customHeight="1" s="1"/>
+    <row r="23" ht="15" customHeight="1" s="1"/>
+    <row r="24" ht="15" customHeight="1" s="1"/>
+    <row r="56" ht="12" customHeight="1" s="1"/>
+    <row r="57" ht="12" customHeight="1" s="1"/>
+    <row r="58" ht="12" customHeight="1" s="1"/>
+    <row r="59" ht="12" customHeight="1" s="1"/>
+    <row r="60" ht="12" customHeight="1" s="1"/>
+    <row r="61" ht="12" customHeight="1" s="1"/>
+    <row r="62" ht="12" customHeight="1" s="1"/>
+    <row r="63" ht="12" customHeight="1" s="1"/>
+    <row r="64" ht="12" customHeight="1" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1067,6 +1067,11 @@
           <t>attribute_point</t>
         </is>
       </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>CMP_rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1089,6 +1094,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1109,6 +1119,11 @@
       <c r="D3" s="0" t="inlineStr">
         <is>
           <t>升级获得加点数</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>魔力召唤增加倍率</t>
         </is>
       </c>
     </row>
@@ -1125,6 +1140,9 @@
       <c r="D4" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="E4" s="0" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
@@ -1139,6 +1157,9 @@
       <c r="D5" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="E5" s="0" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
@@ -1153,6 +1174,9 @@
       <c r="D6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="E6" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
@@ -1167,6 +1191,9 @@
       <c r="D7" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="E7" s="0" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
@@ -1180,6 +1207,9 @@
       </c>
       <c r="D8" s="0" t="n">
         <v>5</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1195,6 +1225,9 @@
       <c r="D9" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="E9" s="0" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
@@ -1209,6 +1242,9 @@
       <c r="D10" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="E10" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
@@ -1223,6 +1259,9 @@
       <c r="D11" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="E11" s="0" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
@@ -1237,6 +1276,9 @@
       <c r="D12" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="E12" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
@@ -1250,6 +1292,9 @@
       </c>
       <c r="D13" s="0" t="n">
         <v>5</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.5" customWidth="1" style="1" min="1" max="1"/>
@@ -1072,6 +1072,11 @@
           <t>CMP_rate</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>level_color</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1099,6 +1104,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1124,6 +1134,11 @@
       <c r="E3" s="0" t="inlineStr">
         <is>
           <t>魔力召唤增加倍率</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>等级颜色</t>
         </is>
       </c>
     </row>
@@ -1143,6 +1158,11 @@
       <c r="E4" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>#9CE07A</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
@@ -1160,6 +1180,11 @@
       <c r="E5" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>#5FD15B</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
@@ -1177,6 +1202,11 @@
       <c r="E6" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>#3FD0A8</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
@@ -1194,6 +1224,11 @@
       <c r="E7" s="0" t="n">
         <v>1.5</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>#36C6E0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
@@ -1210,6 +1245,11 @@
       </c>
       <c r="E8" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>#4FA8FF</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1228,6 +1268,11 @@
       <c r="E9" s="0" t="n">
         <v>2.5</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>#6E83FF</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
@@ -1245,6 +1290,11 @@
       <c r="E10" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>#A86BFF</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
@@ -1262,6 +1312,11 @@
       <c r="E11" s="0" t="n">
         <v>3.5</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>#E85BD1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
@@ -1279,6 +1334,11 @@
       <c r="E12" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>#FF8A3D</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
@@ -1295,6 +1355,11 @@
       </c>
       <c r="E13" s="0" t="n">
         <v>4.5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>#FFC83D</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
@@ -1072,7 +1072,7 @@
           <t>CMP_rate</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>level_color</t>
         </is>
@@ -1104,7 +1104,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1136,7 +1136,7 @@
           <t>魔力召唤增加倍率</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>等级颜色</t>
         </is>
@@ -1150,7 +1150,7 @@
         <v>100</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>5</v>
@@ -1158,7 +1158,7 @@
       <c r="E4" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>#9CE07A</t>
         </is>
@@ -1172,7 +1172,7 @@
         <v>1000</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>5</v>
@@ -1180,7 +1180,7 @@
       <c r="E5" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>#5FD15B</t>
         </is>
@@ -1194,7 +1194,7 @@
         <v>5000</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>5</v>
@@ -1202,7 +1202,7 @@
       <c r="E6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>#3FD0A8</t>
         </is>
@@ -1216,7 +1216,7 @@
         <v>10000</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>5</v>
@@ -1224,7 +1224,7 @@
       <c r="E7" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>#36C6E0</t>
         </is>
@@ -1238,7 +1238,7 @@
         <v>50000</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>5</v>
@@ -1246,7 +1246,7 @@
       <c r="E8" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>#4FA8FF</t>
         </is>
@@ -1260,7 +1260,7 @@
         <v>100000</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>5</v>
@@ -1268,7 +1268,7 @@
       <c r="E9" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>#6E83FF</t>
         </is>
@@ -1290,7 +1290,7 @@
       <c r="E10" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>#A86BFF</t>
         </is>
@@ -1312,7 +1312,7 @@
       <c r="E11" s="0" t="n">
         <v>3.5</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>#E85BD1</t>
         </is>
@@ -1326,7 +1326,7 @@
         <v>5000000</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       <c r="E12" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>#FF8A3D</t>
         </is>
@@ -1348,7 +1348,7 @@
         <v>10000000</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>5</v>
@@ -1356,7 +1356,7 @@
       <c r="E13" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>#FFC83D</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="LevelInfo" sheetId="1" state="visible" r:id="rId1"/>
@@ -1038,12 +1038,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.5" customWidth="1" style="1" min="1" max="1"/>
     <col width="17.5" customWidth="1" style="1" min="2" max="2"/>
     <col width="17.125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="24.875" customWidth="1" style="1" min="4" max="4"/>
+    <col width="22.125" customWidth="1" style="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1077,6 +1079,11 @@
           <t>level_color</t>
         </is>
       </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>juicer_exp</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1109,6 +1116,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1141,35 +1153,43 @@
           <t>等级颜色</t>
         </is>
       </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>榨汁经验(被榨汁时按等级贡献的经验值)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>#9CE07A</t>
-        </is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>2</v>
@@ -1178,42 +1198,48 @@
         <v>5</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>#5FD15B</t>
-        </is>
+          <t>#9CE07A</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>#3FD0A8</t>
-        </is>
+          <t>#5FD15B</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>3</v>
@@ -1222,42 +1248,48 @@
         <v>5</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>#36C6E0</t>
-        </is>
+          <t>#3FD0A8</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>5</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>#4FA8FF</t>
-        </is>
+          <t>#36C6E0</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>4</v>
@@ -1266,42 +1298,48 @@
         <v>5</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>#6E83FF</t>
-        </is>
+          <t>#4FA8FF</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>5</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>#A86BFF</t>
-        </is>
+          <t>#6E83FF</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>5</v>
@@ -1310,42 +1348,48 @@
         <v>5</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>#E85BD1</t>
-        </is>
+          <t>#A86BFF</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>500000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>5</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>#FF8A3D</t>
-        </is>
+          <t>#E85BD1</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>1000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="C13" s="0" t="n">
         <v>6</v>
@@ -1354,15 +1398,42 @@
         <v>5</v>
       </c>
       <c r="E13" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>#FF8A3D</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="1">
+      <c r="A14" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>#FFC83D</t>
         </is>
       </c>
+      <c r="G14" s="0" t="n">
+        <v>10000000</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="1"/>
     <row r="15" ht="15" customHeight="1" s="1"/>
     <row r="16" ht="15" customHeight="1" s="1"/>
     <row r="17" ht="15" customHeight="1" s="1"/>
